--- a/data/trans_camb/P2B_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P2B_R-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>22,94; 38,38</t>
+          <t>22,58; 38,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,94; 25,9</t>
+          <t>9,38; 25,14</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,19; 5,36</t>
+          <t>-13,34; 6,25</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>29,0; 42,26</t>
+          <t>28,03; 42,74</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>22,69; 38,22</t>
+          <t>23,37; 37,53</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 17,76</t>
+          <t>-2,33; 17,06</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,33; 39,15</t>
+          <t>28,2; 38,51</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>18,98; 30,05</t>
+          <t>18,39; 29,58</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 7,83</t>
+          <t>-5,08; 8,86</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>98,44; 244,55</t>
+          <t>96,32; 245,15</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>41,24; 159,65</t>
+          <t>41,73; 163,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-64,22; 33,98</t>
+          <t>-63,5; 39,25</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>144,81; 327,08</t>
+          <t>144,17; 325,84</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>117,83; 304,23</t>
+          <t>118,35; 287,01</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-12,14; 129,87</t>
+          <t>-12,18; 120,97</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>137,44; 261,97</t>
+          <t>138,68; 257,77</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>94,73; 201,72</t>
+          <t>94,35; 197,56</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-29,09; 48,09</t>
+          <t>-26,83; 55,99</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>19,69; 32,61</t>
+          <t>19,01; 32,58</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>19,63; 32,91</t>
+          <t>19,73; 33,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,38; 8,32</t>
+          <t>-10,18; 8,73</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>35,61; 47,27</t>
+          <t>35,78; 47,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>25,22; 37,16</t>
+          <t>24,38; 36,6</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-21,51; 1,25</t>
+          <t>-21,05; 0,65</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>29,19; 38,14</t>
+          <t>30,22; 38,91</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>24,51; 33,73</t>
+          <t>24,45; 33,66</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-14,47; 1,24</t>
+          <t>-15,6; 1,51</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>59,26; 125,5</t>
+          <t>57,85; 123,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>58,55; 125,79</t>
+          <t>59,65; 133,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-32,88; 29,26</t>
+          <t>-33,3; 31,49</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>94,15; 154,11</t>
+          <t>93,36; 155,4</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>66,57; 122,84</t>
+          <t>63,48; 117,13</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-59,83; 3,82</t>
+          <t>-58,46; 2,02</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,24; 128,8</t>
+          <t>88,79; 132,94</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>70,88; 113,48</t>
+          <t>70,94; 114,47</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-45,15; 3,66</t>
+          <t>-45,87; 4,82</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>40,65; 50,99</t>
+          <t>40,23; 51,22</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>28,22; 39,99</t>
+          <t>28,33; 40,35</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 11,23</t>
+          <t>-1,52; 11,53</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>41,47; 51,37</t>
+          <t>42,05; 51,55</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>29,93; 40,37</t>
+          <t>30,03; 40,61</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-11,27; 2,26</t>
+          <t>-11,78; 2,13</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,97; 49,81</t>
+          <t>42,61; 50,06</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>30,73; 38,26</t>
+          <t>30,66; 38,41</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-5,31; 4,33</t>
+          <t>-4,75; 5,05</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>131,6; 215,29</t>
+          <t>134,39; 223,65</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>93,07; 165,58</t>
+          <t>94,34; 169,51</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-4,35; 45,6</t>
+          <t>-4,95; 48,19</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>125,64; 191,89</t>
+          <t>128,54; 192,59</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>91,48; 150,49</t>
+          <t>91,29; 150,15</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-34,99; 7,77</t>
+          <t>-37,85; 7,11</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>138,1; 187,82</t>
+          <t>137,65; 188,38</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>99,43; 143,02</t>
+          <t>99,32; 145,81</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-17,51; 15,76</t>
+          <t>-16,11; 18,41</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>32,8; 44,66</t>
+          <t>32,91; 44,73</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>19,11; 30,42</t>
+          <t>18,25; 30,05</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,07; 13,08</t>
+          <t>2,83; 13,56</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19,03; 31,52</t>
+          <t>19,14; 31,09</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>15,63; 27,41</t>
+          <t>15,42; 27,33</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 7,31</t>
+          <t>-3,92; 7,31</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,65; 36,34</t>
+          <t>27,38; 35,7</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>18,63; 26,72</t>
+          <t>18,4; 26,67</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,26; 8,58</t>
+          <t>0,85; 8,2</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>167,47; 331,29</t>
+          <t>171,57; 343,81</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>97,51; 224,72</t>
+          <t>93,76; 217,06</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11,18; 99,01</t>
+          <t>15,03; 109,34</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>81,74; 189,15</t>
+          <t>87,42; 191,22</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>70,17; 168,55</t>
+          <t>71,2; 162,75</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-16,22; 44,7</t>
+          <t>-16,82; 44,38</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>139,22; 232,95</t>
+          <t>138,33; 226,73</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>93,72; 171,12</t>
+          <t>93,47; 173,42</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>6,54; 52,91</t>
+          <t>4,34; 51,54</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>9,03; 22,03</t>
+          <t>9,31; 21,86</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,11; 15,25</t>
+          <t>3,0; 15,24</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 10,09</t>
+          <t>-1,49; 10,26</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5,27; 18,33</t>
+          <t>4,77; 18,11</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 12,12</t>
+          <t>-0,49; 12,5</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-6,54; 4,58</t>
+          <t>-7,1; 3,69</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8,66; 17,92</t>
+          <t>9,0; 17,93</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2,89; 11,91</t>
+          <t>3,1; 11,98</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 5,37</t>
+          <t>-2,49; 5,85</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>48,36; 182,9</t>
+          <t>52,22; 188,41</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>16,43; 129,57</t>
+          <t>15,15; 121,31</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-5,33; 85,45</t>
+          <t>-8,69; 86,46</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>21,26; 101,58</t>
+          <t>20,5; 102,84</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 69,69</t>
+          <t>-1,92; 74,03</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-27,32; 26,94</t>
+          <t>-28,24; 20,26</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>42,2; 112,78</t>
+          <t>43,55; 115,04</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>13,95; 75,69</t>
+          <t>15,69; 75,81</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-11,97; 34,1</t>
+          <t>-12,64; 37,36</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>8,1; 21,76</t>
+          <t>8,85; 22,08</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>2,21; 14,82</t>
+          <t>2,23; 14,2</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-7,83; 1,89</t>
+          <t>-7,44; 1,71</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 9,53</t>
+          <t>-4,15; 8,24</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 9,91</t>
+          <t>-2,87; 10,0</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-8,89; 54,58</t>
+          <t>-9,53; 55,62</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,55; 13,05</t>
+          <t>3,5; 12,99</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>0,82; 10,11</t>
+          <t>1,04; 9,77</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-6,12; 45,13</t>
+          <t>-6,31; 45,18</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>44,35; 198,7</t>
+          <t>51,75; 194,86</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>10,88; 133,03</t>
+          <t>13,5; 127,11</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-44,26; 16,91</t>
+          <t>-43,36; 14,48</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-12,31; 48,7</t>
+          <t>-15,49; 38,98</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-10,51; 48,41</t>
+          <t>-10,61; 50,42</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-36,35; 258,1</t>
+          <t>-37,94; 257,24</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>16,83; 77,23</t>
+          <t>16,7; 75,84</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>4,18; 60,42</t>
+          <t>4,41; 55,59</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-30,96; 246,52</t>
+          <t>-31,54; 240,68</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>8,88; 27,29</t>
+          <t>9,02; 27,33</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0,27; 15,73</t>
+          <t>0,23; 16,64</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-6,31; 8,33</t>
+          <t>-6,68; 8,64</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>9,84; 25,2</t>
+          <t>9,87; 25,29</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>7,74; 23,72</t>
+          <t>8,36; 23,85</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,55; 18,02</t>
+          <t>3,99; 17,16</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>12,64; 24,19</t>
+          <t>12,19; 23,52</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>6,75; 18,5</t>
+          <t>7,5; 18,96</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2,27; 11,98</t>
+          <t>2,59; 12,25</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>26,13; 115,16</t>
+          <t>27,29; 116,22</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>0,77; 68,44</t>
+          <t>0,6; 70,58</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-19,59; 36,2</t>
+          <t>-19,69; 35,91</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>26,84; 87,0</t>
+          <t>26,88; 88,79</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>20,27; 82,81</t>
+          <t>22,07; 84,71</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>14,9; 65,44</t>
+          <t>11,04; 61,68</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>36,72; 87,47</t>
+          <t>36,65; 87,07</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>19,79; 65,53</t>
+          <t>22,27; 67,21</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>6,29; 43,24</t>
+          <t>7,35; 44,49</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>27,45; 32,49</t>
+          <t>27,2; 32,3</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>17,05; 22,27</t>
+          <t>17,23; 22,45</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 3,51</t>
+          <t>-1,1; 3,61</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>25,42; 30,36</t>
+          <t>25,58; 30,47</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>18,14; 23,18</t>
+          <t>18,41; 23,39</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 20,34</t>
+          <t>-1,32; 22,42</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>27,12; 30,64</t>
+          <t>27,11; 30,69</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>18,53; 22,07</t>
+          <t>18,61; 22,06</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 13,71</t>
+          <t>-0,44; 13,45</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>119,86; 159,06</t>
+          <t>116,73; 157,04</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>73,94; 108,89</t>
+          <t>74,92; 109,56</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-6,21; 17,22</t>
+          <t>-5,03; 17,72</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>92,78; 122,01</t>
+          <t>93,03; 121,8</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>66,52; 92,55</t>
+          <t>67,15; 93,4</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-4,81; 76,87</t>
+          <t>-5,01; 87,69</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>107,43; 131,19</t>
+          <t>108,24; 132,25</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>73,85; 94,31</t>
+          <t>74,07; 94,77</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 55,7</t>
+          <t>-1,95; 58,2</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2B_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P2B_R-Edad-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-4,93</t>
+          <t>-0,75</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,0</t>
+          <t>9,73</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,75</t>
+          <t>4,68</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>22,58; 38,2</t>
+          <t>22,53; 38,68</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,38; 25,14</t>
+          <t>9,25; 25,96</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,34; 6,25</t>
+          <t>-10,02; 11,57</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28,03; 42,74</t>
+          <t>29,54; 43,17</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>23,37; 37,53</t>
+          <t>23,49; 38,16</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 17,06</t>
+          <t>0,82; 20,33</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,2; 38,51</t>
+          <t>28,14; 38,65</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>18,39; 29,58</t>
+          <t>19,32; 29,89</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-5,08; 8,86</t>
+          <t>-1,89; 12,02</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-25,49%</t>
+          <t>-3,9%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>43,89%</t>
+          <t>61,03%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>26,75%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>96,32; 245,15</t>
+          <t>97,69; 245,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>41,73; 163,67</t>
+          <t>38,33; 158,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-63,5; 39,25</t>
+          <t>-47,44; 67,71</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>144,17; 325,84</t>
+          <t>148,9; 353,61</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>118,35; 287,01</t>
+          <t>117,89; 296,35</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-12,18; 120,97</t>
+          <t>2,59; 148,0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>138,68; 257,77</t>
+          <t>136,22; 256,35</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>94,35; 197,56</t>
+          <t>96,8; 200,94</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-26,83; 55,99</t>
+          <t>-10,36; 75,8</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-1,78</t>
+          <t>1,92</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-7,8</t>
+          <t>-0,8</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-5,12</t>
+          <t>0,63</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>19,01; 32,58</t>
+          <t>19,2; 31,84</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>19,73; 33,98</t>
+          <t>18,91; 33,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,18; 8,73</t>
+          <t>-6,66; 11,3</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>35,78; 47,21</t>
+          <t>36,01; 47,55</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>24,38; 36,6</t>
+          <t>24,5; 37,27</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-21,05; 0,65</t>
+          <t>-6,71; 6,83</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>30,22; 38,91</t>
+          <t>29,66; 38,55</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>24,45; 33,66</t>
+          <t>24,44; 33,67</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-15,6; 1,51</t>
+          <t>-4,76; 6,48</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-6,04%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-22,61%</t>
+          <t>-2,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-15,92%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>57,85; 123,94</t>
+          <t>57,72; 124,18</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>59,65; 133,13</t>
+          <t>58,04; 127,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-33,3; 31,49</t>
+          <t>-21,52; 42,8</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>93,36; 155,4</t>
+          <t>95,89; 154,23</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>63,48; 117,13</t>
+          <t>65,56; 121,38</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-58,46; 2,02</t>
+          <t>-18,32; 21,88</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,79; 132,94</t>
+          <t>86,04; 130,86</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>70,94; 114,47</t>
+          <t>71,11; 112,42</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-45,87; 4,82</t>
+          <t>-14,56; 21,38</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4,7</t>
+          <t>5,96</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-3,33</t>
+          <t>-0,33</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,19</t>
+          <t>2,53</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>40,23; 51,22</t>
+          <t>40,76; 51,01</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>28,33; 40,35</t>
+          <t>27,4; 39,53</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 11,53</t>
+          <t>-0,34; 11,99</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>42,05; 51,55</t>
+          <t>41,36; 51,89</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>30,03; 40,61</t>
+          <t>30,32; 40,73</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-11,78; 2,13</t>
+          <t>-5,13; 4,78</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,61; 50,06</t>
+          <t>42,89; 50,07</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>30,66; 38,41</t>
+          <t>30,74; 38,63</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 5,05</t>
+          <t>-1,44; 6,43</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-11,1%</t>
+          <t>-1,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>8,84%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>134,39; 223,65</t>
+          <t>133,34; 214,79</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>94,34; 169,51</t>
+          <t>89,76; 165,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-4,95; 48,19</t>
+          <t>-1,53; 49,08</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>128,54; 192,59</t>
+          <t>124,4; 194,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>91,29; 150,15</t>
+          <t>92,15; 150,39</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-37,85; 7,11</t>
+          <t>-15,8; 17,21</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>137,65; 188,38</t>
+          <t>138,06; 190,34</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>99,32; 145,81</t>
+          <t>99,97; 145,95</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-16,11; 18,41</t>
+          <t>-4,59; 24,41</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7,91</t>
+          <t>8,89</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,15</t>
+          <t>4,74</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>4,92</t>
+          <t>6,78</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>32,91; 44,73</t>
+          <t>32,72; 44,54</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>18,25; 30,05</t>
+          <t>18,66; 30,94</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,83; 13,56</t>
+          <t>3,39; 15,05</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19,14; 31,09</t>
+          <t>19,46; 31,4</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>15,42; 27,33</t>
+          <t>14,76; 27,1</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 7,31</t>
+          <t>0,03; 9,47</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,38; 35,7</t>
+          <t>27,39; 36,2</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>18,4; 26,67</t>
+          <t>18,64; 27,02</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,85; 8,2</t>
+          <t>3,16; 10,31</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>48,99%</t>
+          <t>55,08%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>38,12%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>171,57; 343,81</t>
+          <t>165,67; 340,36</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>93,76; 217,06</t>
+          <t>97,49; 230,84</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>15,03; 109,34</t>
+          <t>17,99; 116,21</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>87,42; 191,22</t>
+          <t>88,04; 193,79</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>71,2; 162,75</t>
+          <t>66,24; 166,85</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-16,82; 44,38</t>
+          <t>0,1; 57,77</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>138,33; 226,73</t>
+          <t>136,55; 230,17</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>93,47; 173,42</t>
+          <t>93,99; 170,59</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4,34; 51,54</t>
+          <t>15,32; 64,21</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4,64</t>
+          <t>4,84</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-1,22</t>
+          <t>-1,17</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>1,6</t>
+          <t>1,72</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>9,31; 21,86</t>
+          <t>8,68; 21,47</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,0; 15,24</t>
+          <t>3,27; 15,07</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 10,26</t>
+          <t>-0,86; 10,53</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,77; 18,11</t>
+          <t>4,5; 17,68</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 12,5</t>
+          <t>-0,76; 12,26</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-7,1; 3,69</t>
+          <t>-6,51; 3,93</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,0; 17,93</t>
+          <t>8,74; 17,75</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3,1; 11,98</t>
+          <t>2,51; 11,35</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 5,85</t>
+          <t>-2,11; 5,68</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>33,04%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-5,86%</t>
+          <t>-5,63%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,64%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>52,22; 188,41</t>
+          <t>49,06; 176,95</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>15,15; 121,31</t>
+          <t>18,13; 128,13</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-8,69; 86,46</t>
+          <t>-6,91; 88,51</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>20,5; 102,84</t>
+          <t>17,94; 101,74</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 74,03</t>
+          <t>-3,48; 69,21</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-28,24; 20,26</t>
+          <t>-26,52; 22,72</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>43,55; 115,04</t>
+          <t>44,13; 113,15</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>15,69; 75,81</t>
+          <t>12,26; 71,65</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-12,64; 37,36</t>
+          <t>-10,28; 37,12</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-2,53</t>
+          <t>-2,68</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>20,77</t>
+          <t>-6,96</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>12,84</t>
+          <t>-5,09</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>8,85; 22,08</t>
+          <t>8,41; 22,26</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>2,23; 14,2</t>
+          <t>1,82; 14,11</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-7,44; 1,71</t>
+          <t>-7,21; 2,0</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 8,24</t>
+          <t>-3,73; 8,49</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 10,0</t>
+          <t>-2,51; 10,02</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-9,53; 55,62</t>
+          <t>-12,27; -1,95</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,5; 12,99</t>
+          <t>4,03; 13,09</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>1,04; 9,77</t>
+          <t>1,39; 9,9</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-6,31; 45,18</t>
+          <t>-8,92; -1,86</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-17,85%</t>
+          <t>-18,9%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>-29,42%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>66,56%</t>
+          <t>-26,39%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>51,75; 194,86</t>
+          <t>48,49; 195,83</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>13,5; 127,11</t>
+          <t>10,17; 122,44</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-43,36; 14,48</t>
+          <t>-42,7; 18,44</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-15,49; 38,98</t>
+          <t>-14,19; 40,28</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-10,61; 50,42</t>
+          <t>-9,78; 48,5</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-37,94; 257,24</t>
+          <t>-44,91; -10,02</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>16,7; 75,84</t>
+          <t>18,77; 78,4</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>4,41; 55,59</t>
+          <t>5,6; 57,76</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-31,54; 240,68</t>
+          <t>-40,42; -10,55</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1,55</t>
+          <t>1,01</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>11,23</t>
+          <t>11,0</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>7,32</t>
+          <t>6,95</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>9,02; 27,33</t>
+          <t>8,04; 27,19</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0,23; 16,64</t>
+          <t>-0,14; 15,88</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-6,68; 8,64</t>
+          <t>-7,79; 7,09</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>9,87; 25,29</t>
+          <t>9,85; 25,22</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>8,36; 23,85</t>
+          <t>7,82; 23,87</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,99; 17,16</t>
+          <t>5,02; 17,02</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>12,19; 23,52</t>
+          <t>11,47; 23,32</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>7,5; 18,96</t>
+          <t>6,91; 18,5</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2,59; 12,25</t>
+          <t>2,02; 11,86</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>33,98%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>22,56%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>27,29; 116,22</t>
+          <t>24,58; 113,21</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>0,6; 70,58</t>
+          <t>-0,45; 64,78</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-19,69; 35,91</t>
+          <t>-23,22; 29,72</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>26,88; 88,79</t>
+          <t>26,97; 90,97</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>22,07; 84,71</t>
+          <t>21,41; 85,88</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11,04; 61,68</t>
+          <t>13,27; 61,1</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>36,65; 87,07</t>
+          <t>33,86; 83,4</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>22,27; 67,21</t>
+          <t>21,04; 67,45</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>7,35; 44,49</t>
+          <t>5,9; 42,99</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1,04</t>
+          <t>2,21</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>4,66</t>
+          <t>1,53</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>3,28</t>
+          <t>1,88</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>27,2; 32,3</t>
+          <t>27,12; 32,6</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>17,23; 22,45</t>
+          <t>17,05; 22,44</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 3,61</t>
+          <t>-0,45; 4,65</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>25,58; 30,47</t>
+          <t>25,8; 30,42</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>18,41; 23,39</t>
+          <t>18,2; 23,1</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 22,42</t>
+          <t>-0,67; 3,66</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>27,11; 30,69</t>
+          <t>26,97; 30,5</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>18,61; 22,06</t>
+          <t>18,25; 21,98</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 13,45</t>
+          <t>0,25; 3,48</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>7,77%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>116,73; 157,04</t>
+          <t>117,32; 159,14</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>74,92; 109,56</t>
+          <t>73,49; 108,72</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 17,72</t>
+          <t>-1,61; 22,91</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>93,03; 121,8</t>
+          <t>93,74; 123,11</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>67,15; 93,4</t>
+          <t>66,44; 92,38</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-5,01; 87,69</t>
+          <t>-2,43; 14,72</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>108,24; 132,25</t>
+          <t>107,28; 131,06</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>74,07; 94,77</t>
+          <t>73,18; 94,43</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 58,2</t>
+          <t>0,97; 14,89</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2B_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P2B_R-Edad-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas que requieren dedicación o cuidados especiales</t>
+          <t>Población que convive con personas que requieren dedicación o cuidados especiales</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
